--- a/data/trans_orig/IP37-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26415</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40652</t>
+          <t>40775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>60140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75965</t>
+          <t>76447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22628</t>
+          <t>22824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>34950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51808</t>
+          <t>51257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110843</t>
+          <t>112184</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133637</t>
+          <t>132658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125365</t>
+          <t>125463</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148917</t>
+          <t>148890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>242472</t>
+          <t>243581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273708</t>
+          <t>274772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62059</t>
+          <t>63038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84853</t>
+          <t>83512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74379</t>
+          <t>74406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97931</t>
+          <t>97833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145285</t>
+          <t>144221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176521</t>
+          <t>175412</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34717</t>
+          <t>34595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32649</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50646</t>
+          <t>50263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64732</t>
+          <t>64269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23310</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37396</t>
+          <t>37779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>171440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197088</t>
+          <t>198509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>188033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214065</t>
+          <t>215929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>365387</t>
+          <t>366403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404206</t>
+          <t>403945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>102979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131032</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102878</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129723</t>
+          <t>128910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214225</t>
+          <t>214486</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253044</t>
+          <t>252028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51286</t>
+          <t>50710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>35605</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>48183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77827</t>
+          <t>77979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95079</t>
+          <t>95771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>33903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>51695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194467</t>
+          <t>194146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216740</t>
+          <t>216588</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201630</t>
+          <t>201652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225450</t>
+          <t>225647</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>404876</t>
+          <t>404647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>436359</t>
+          <t>436674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44088</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66361</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61450</t>
+          <t>61253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85270</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111368</t>
+          <t>111053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142851</t>
+          <t>143080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53017</t>
+          <t>53214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40929</t>
+          <t>41533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52785</t>
+          <t>52874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>86349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102720</t>
+          <t>102936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23027</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>39398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>284784</t>
+          <t>284619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>312239</t>
+          <t>312540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288350</t>
+          <t>286906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>318207</t>
+          <t>317355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>582017</t>
+          <t>581685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>621744</t>
+          <t>622421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>76557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104313</t>
+          <t>104478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95845</t>
+          <t>96697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125702</t>
+          <t>127146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>181405</t>
+          <t>180728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221132</t>
+          <t>221464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29921</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39372</t>
+          <t>39842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60444</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75249</t>
+          <t>75765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183799</t>
+          <t>181259</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>204965</t>
+          <t>204909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175091</t>
+          <t>176176</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>199508</t>
+          <t>199076</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>366228</t>
+          <t>365283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>397058</t>
+          <t>398616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>52561</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73671</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59511</t>
+          <t>59943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83928</t>
+          <t>82843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119431</t>
+          <t>117873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>150261</t>
+          <t>151206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40930</t>
+          <t>40693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>41360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>51568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>86558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100951</t>
+          <t>100792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16005</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30579</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>262856</t>
+          <t>263178</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288726</t>
+          <t>289108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255559</t>
+          <t>254604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>283291</t>
+          <t>282717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>525049</t>
+          <t>526669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>563719</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73603</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>99151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83551</t>
+          <t>84125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165452</t>
+          <t>164668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204122</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17262</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28874</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43833</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59069</t>
+          <t>58173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17210</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122292</t>
+          <t>122725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160793</t>
+          <t>163602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118311</t>
+          <t>119017</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>143694</t>
+          <t>142551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249198</t>
+          <t>249116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295127</t>
+          <t>297827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78750</t>
+          <t>78317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49900</t>
+          <t>51043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75283</t>
+          <t>74577</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99508</t>
+          <t>96808</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145437</t>
+          <t>145519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>16163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>21339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>16147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>34300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>43814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162495</t>
+          <t>163670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204839</t>
+          <t>205255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162932</t>
+          <t>164795</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192773</t>
+          <t>193078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338564</t>
+          <t>339051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390416</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>63346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>91629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123652</t>
+          <t>125858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175504</t>
+          <t>175017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP37-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35955</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30211</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41382</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32340</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26415</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38728</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26038</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>38436</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>55,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35955</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>29847</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>40775</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60140</t>
+          <t>60456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76447</t>
+          <t>76339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,53%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16716</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11289</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22460</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26386</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19998</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32311</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20290</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>32688</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,93%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16716</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11896</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22824</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51257</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>52671</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>52671</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>52671</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>52671</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>52671</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>52671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>136998</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124784</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>148001</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>55,88%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>122387</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>112184</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>132658</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>110397</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>132271</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>62,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>67,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>136998</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>125463</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>148890</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>243581</t>
+          <t>241346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>274772</t>
+          <t>275902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86298</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75295</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>98512</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>44,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>73309</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>63038</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83512</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>63425</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>85299</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>37,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86298</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>74406</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>38,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144221</t>
+          <t>143091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175412</t>
+          <t>177647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223296</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223296</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223296</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>293</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195696</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195696</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195696</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223296</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223296</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223296</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28046</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23240</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32122</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>68,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>29574</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23754</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34595</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>23865</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>34779</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>28046</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>22771</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>32181</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>68,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50263</t>
+          <t>49701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64269</t>
+          <t>64090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12930</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8854</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17736</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>17492</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12471</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23312</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12287</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23201</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12930</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8795</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18205</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23773</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40976</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40976</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40976</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>47066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>47066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>47066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40976</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>40976</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>40976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>186230</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>213697</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>184301</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>171440</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>198509</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>171439</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>199853</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>56,86%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>200999</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>188033</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>215929</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>59,33%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>366403</t>
+          <t>364768</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>403945</t>
+          <t>404199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>115944</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>103246</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130713</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>117187</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>102979</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>130048</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>101635</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>130049</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>38,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>43,14%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>115944</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>101014</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>128910</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>40,67%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>350</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214486</t>
+          <t>214232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252028</t>
+          <t>253663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>301488</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41984</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34761</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47590</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45104</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38469</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50710</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>38323</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51019</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>68,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41984</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>35605</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48183</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77979</t>
+          <t>77434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95771</t>
+          <t>95366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21982</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16376</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29205</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20605</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14999</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27240</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14690</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27386</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21982</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15783</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28361</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>34308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51695</t>
+          <t>52240</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>63966</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>63966</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63966</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>65709</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>65709</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>65709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>63966</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>63966</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>63966</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>214194</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>201951</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>226535</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>74,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>70,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>206436</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>194146</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>216588</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>194295</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>216330</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>79,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>83,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>214194</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>201652</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>225647</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>74,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>404647</t>
+          <t>402304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>436674</t>
+          <t>436277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72706</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60365</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84949</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>54392</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>44240</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66682</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44498</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>66533</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>72706</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>61253</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>85248</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>25,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111053</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143080</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>286900</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>286900</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>286900</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>260828</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>260828</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>260828</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>286900</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>286900</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>286900</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47403</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41030</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52579</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>75,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48017</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>41665</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53214</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>41336</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>53158</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>76,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47403</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>41533</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>52874</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>75,02%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86349</t>
+          <t>85788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102936</t>
+          <t>103030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15784</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10608</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22157</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>14544</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9347</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20896</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21225</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,25%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>15784</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>10313</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21654</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>24,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39398</t>
+          <t>39959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -3243,52 +3243,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>63187</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>62561</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>62561</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>62561</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>63187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>303581</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>288453</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>318785</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>434</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>284619</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>312540</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>285815</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>312603</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>303581</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>286906</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>317355</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>73,32%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>581685</t>
+          <t>584383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>622421</t>
+          <t>624947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>110471</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95267</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>125599</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>89541</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76557</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>104478</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>76494</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>103282</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>110471</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>96697</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>127146</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180728</t>
+          <t>178202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221464</t>
+          <t>218766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>414052</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>414052</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>414052</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>559</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>389097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>389097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>389097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>414052</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>414052</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>414052</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33099</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26751</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38129</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35406</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30302</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39842</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28989</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39623</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>76,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33099</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27057</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38490</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>67,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75765</t>
+          <t>75724</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16053</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11023</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22401</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11168</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6732</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16272</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6951</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17585</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16053</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10662</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22095</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19961</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34615</t>
+          <t>34999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49152</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49152</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49152</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46574</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46574</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46574</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>49152</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49152</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>187918</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>176245</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>199717</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>77,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>194765</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>181259</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>204909</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>183258</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>206181</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>75,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>79,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>187918</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>176176</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>199076</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>72,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>365283</t>
+          <t>366171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>398616</t>
+          <t>397676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71101</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59302</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82774</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>62705</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52561</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76211</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>51289</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>74212</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>24,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>71101</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>59943</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>82843</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117873</t>
+          <t>118813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151206</t>
+          <t>150318</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>259019</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>259019</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>259019</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>389</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>257470</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>257470</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>257470</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>259019</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>259019</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>259019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47459</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42023</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52255</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>71,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46642</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40693</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50828</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40837</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51125</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>80,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47459</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>41360</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51568</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>80,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86558</t>
+          <t>86416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100792</t>
+          <t>100996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>11213</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6417</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16649</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>28,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>11642</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7456</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17591</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7159</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17447</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>19,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11213</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7104</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>17312</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>58672</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>58672</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>58672</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>58284</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>58284</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>58284</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>58672</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>58672</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>58672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,74 +4958,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>254378</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>281816</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>69,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>420</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>276814</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>263178</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>289108</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>262174</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>289089</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>79,79%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>254604</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>282717</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>69,4%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>77,07%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>802</t>
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526669</t>
+          <t>525292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564503</t>
+          <t>563262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98366</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>85026</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>112464</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>85515</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73221</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>99151</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73240</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>100155</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>23,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98366</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84125</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>112238</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164668</t>
+          <t>165909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>203879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>544</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>362329</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>362329</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>362329</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25813</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20245</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29751</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23353</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17471</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29220</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>67,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>35021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58173</t>
+          <t>48367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9654</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15222</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11119</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5252</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17001</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14214</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35467</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35467</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35467</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>34472</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>34472</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34472</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>72387</t>
+          <t>63519</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72387</t>
+          <t>63519</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72387</t>
+          <t>63519</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>117106</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>104592</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>127349</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>137584</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>122725</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>163602</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>68,44%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>81,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>131625</t>
+          <t>108836</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119017</t>
+          <t>97475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142551</t>
+          <t>118729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>269208</t>
+          <t>225941</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249116</t>
+          <t>211044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297827</t>
+          <t>241786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59547</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49304</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72061</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>63458</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37440</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>78317</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61969</t>
+          <t>64077</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51043</t>
+          <t>54184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74577</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>125427</t>
+          <t>123625</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96808</t>
+          <t>107780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145519</t>
+          <t>138522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>176653</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>176653</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>176653</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>201042</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>201042</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>201042</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>193594</t>
+          <t>172913</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193594</t>
+          <t>172913</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>193594</t>
+          <t>172913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>394635</t>
+          <t>349566</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>394635</t>
+          <t>349566</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>394635</t>
+          <t>349566</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19538</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14878</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21913</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19520</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16163</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21339</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>88,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23867</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40196</t>
+          <t>38915</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>33990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43814</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45084</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45084</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>45084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>162456</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>150383</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>175572</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>63,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>74,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>180457</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>163670</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>205255</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164795</t>
+          <t>131478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>193078</t>
+          <t>155723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>307143</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339051</t>
+          <t>289848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388210</t>
+          <t>326240</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72616</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>59500</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>84689</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>77187</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52389</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93974</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>78410</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63346</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91629</t>
+          <t>91619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>153647</t>
+          <t>151026</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125858</t>
+          <t>131929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175017</t>
+          <t>168321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
